--- a/data/RTS-GMLC/Power_Storage.xlsx
+++ b/data/RTS-GMLC/Power_Storage.xlsx
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="U8" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" s="15" t="n">
-        <v>1</v>
+        <v>33367.66</v>
       </c>
       <c r="W8" s="14" t="n">
         <v>3</v>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="AD8" s="18" t="inlineStr">
         <is>
-          <t>RTS-GMLC-storage-placeholder</t>
+          <t>RTS-GMLC-storage-battery-ise</t>
         </is>
       </c>
     </row>
@@ -4445,10 +4445,10 @@
         <v>1</v>
       </c>
       <c r="U8" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" s="15" t="n">
-        <v>1</v>
+        <v>33367.66</v>
       </c>
       <c r="W8" s="14" t="n">
         <v>3</v>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="AD8" s="18" t="inlineStr">
         <is>
-          <t>RTS-GMLC-storage-placeholder</t>
+          <t>RTS-GMLC-storage-battery-ise</t>
         </is>
       </c>
     </row>
